--- a/output/pdf_financials_xlsx/ELBM.xlsx
+++ b/output/pdf_financials_xlsx/ELBM.xlsx
@@ -3969,34 +3969,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.803046</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.834934</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>13.71497</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>16.554</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>17.892</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>25.579</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>26.848</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>33.143</v>
       </c>
     </row>
     <row r="93">
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -7314,7 +7314,11 @@
           <t>Reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8060,7 +8064,11 @@
           <t>Reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -9554,7 +9562,11 @@
           <t>Reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -11064,7 +11076,11 @@
           <t>Reserve (Note 16 and 17)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -11518,7 +11534,11 @@
           <t>Reserve (Note 13 and 14)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -12740,7 +12760,11 @@
           <t>Reserve (Note 11 and 12) 1,803,046</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -13826,7 +13850,11 @@
           <t>Reserve (Note 11 and 12)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -14626,7 +14654,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>0.2</v>
       </c>
@@ -16864,7 +16896,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -18950,7 +18986,11 @@
           <t>Incurring of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -27319,10 +27359,10 @@
         </is>
       </c>
       <c r="H334" s="5" t="n">
-        <v>0.241895</v>
+        <v>-0.241895</v>
       </c>
       <c r="I334" s="5" t="n">
-        <v>0.241895</v>
+        <v>-0.241895</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ELBM.xlsx
+++ b/output/pdf_financials_xlsx/ELBM.xlsx
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.006577</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.003815</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.006577</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.003815</v>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.006577</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -50888,7 +50888,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELBM.xlsx
+++ b/output/pdf_financials_xlsx/ELBM.xlsx
@@ -3040,19 +3040,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.102175</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.50575</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.609855</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.134961</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.056994</v>
+        <v>0.159169</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.230479</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.214035</v>
+        <v>0.11186</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0.131785</v>
@@ -4213,7 +4213,7 @@
         <v>-104.496899</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>12.551</v>
+        <v>-34.916</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>12.551</v>
@@ -4509,7 +4509,7 @@
         <v>1.384904</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.731</v>
+        <v>2.744</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>1.282</v>
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>51.884</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>1.008</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="111">
@@ -4762,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-1.278231</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>2.658474</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -4805,19 +4805,19 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="116">
@@ -15296,7 +15296,11 @@
           <t>Accretion (Notes 9, 10 and 12, 13)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -15876,7 +15880,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -16834,7 +16842,11 @@
           <t>Proceeds from sale of marketable securities (Note 8)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -17158,7 +17170,11 @@
           <t>Transaction costs private placement 2022</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -18398,7 +18414,11 @@
           <t>Accretion (Notes 9, 10 and 11)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -19508,7 +19528,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -20866,7 +20890,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -21192,7 +21220,11 @@
           <t>Transaction costs private placement</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -24056,7 +24088,11 @@
           <t>Share based payment expense - - 1,282 -</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -24714,7 +24750,11 @@
           <t>Share based payment expense - - 731 -</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -26218,7 +26258,11 @@
           <t>Sale (Purchase) of marketable securities</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
